--- a/output/laminas_comunales/comunal_i_ingr_median_a_2024_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2024_valparaiso.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>6.918481233256402</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>7.225065208215709</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>5.757030936118923</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>6.993520097335426</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>5.604310723920491</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>-1.978084084272658</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>8.076289855072471</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>7.341900726796569</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,9 +552,6 @@
       <c r="E10">
         <v>7.961528185947109</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -603,9 +571,6 @@
       <c r="E11">
         <v>6.993468730015451</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -625,9 +590,6 @@
       <c r="E12">
         <v>7.069287832061244</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -647,9 +609,6 @@
       <c r="E13">
         <v>6.756297124372668</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -669,9 +628,6 @@
       <c r="E14">
         <v>7.788408318178219</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -691,9 +647,6 @@
       <c r="E15">
         <v>7.832677548651135</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -713,9 +666,6 @@
       <c r="E16">
         <v>8.976256354159972</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -735,9 +685,6 @@
       <c r="E17">
         <v>10.08962601626015</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -757,9 +704,6 @@
       <c r="E18">
         <v>8.912683979784752</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -779,9 +723,6 @@
       <c r="E19">
         <v>7.251924901497442</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -801,9 +742,6 @@
       <c r="E20">
         <v>7.945857317376182</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -823,9 +761,6 @@
       <c r="E21">
         <v>9.35659016393442</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -845,9 +780,6 @@
       <c r="E22">
         <v>6.959498556010768</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -867,9 +799,6 @@
       <c r="E23">
         <v>8.299212598425187</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -889,9 +818,6 @@
       <c r="E24">
         <v>7.046543688045692</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -911,9 +837,6 @@
       <c r="E25">
         <v>5.134534363772647</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -933,9 +856,6 @@
       <c r="E26">
         <v>8.034207884845369</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -955,9 +875,6 @@
       <c r="E27">
         <v>6.778997915226359</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -977,9 +894,6 @@
       <c r="E28">
         <v>7.049934886452314</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -999,9 +913,6 @@
       <c r="E29">
         <v>6.02766101694916</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1021,9 +932,6 @@
       <c r="E30">
         <v>8.460176966522749</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1043,9 +951,6 @@
       <c r="E31">
         <v>8.488717173413974</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1065,9 +970,6 @@
       <c r="E32">
         <v>6.224032530220458</v>
       </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1087,9 +989,6 @@
       <c r="E33">
         <v>9.360743613138677</v>
       </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1109,9 +1008,6 @@
       <c r="E34">
         <v>7.281587386050159</v>
       </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1131,9 +1027,6 @@
       <c r="E35">
         <v>5.965429717964343</v>
       </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1153,9 +1046,6 @@
       <c r="E36">
         <v>9.260226245047697</v>
       </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1175,9 +1065,6 @@
       <c r="E37">
         <v>6.694807618309162</v>
       </c>
-      <c r="F37" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1197,9 +1084,6 @@
       <c r="E38">
         <v>7.811154629069517</v>
       </c>
-      <c r="F38" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1218,9 +1102,6 @@
       </c>
       <c r="E39">
         <v>9.473399133365422</v>
-      </c>
-      <c r="F39" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2024_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2024_valparaiso.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -480,7 +480,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Juan Fernandez</t>
+          <t>Juan Fernández</t>
         </is>
       </c>
       <c r="B7">
@@ -651,456 +651,475 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B16">
-        <v>846800</v>
+        <v>856320</v>
       </c>
       <c r="C16">
-        <v>777050</v>
+        <v>794428</v>
       </c>
       <c r="D16">
-        <v>69750</v>
+        <v>61892</v>
       </c>
       <c r="E16">
-        <v>8.976256354159972</v>
+        <v>7.790762661940409</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Algarrobo</t>
         </is>
       </c>
       <c r="B17">
-        <v>846314</v>
+        <v>846800</v>
       </c>
       <c r="C17">
-        <v>768750</v>
+        <v>777050</v>
       </c>
       <c r="D17">
-        <v>77564</v>
+        <v>69750</v>
       </c>
       <c r="E17">
-        <v>10.08962601626015</v>
+        <v>8.976256354159972</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Calera</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="B18">
-        <v>845646</v>
+        <v>846314</v>
       </c>
       <c r="C18">
-        <v>776444</v>
+        <v>768750</v>
       </c>
       <c r="D18">
-        <v>69202</v>
+        <v>77564</v>
       </c>
       <c r="E18">
-        <v>8.912683979784752</v>
+        <v>10.08962601626015</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Quintero</t>
+          <t>Calera</t>
         </is>
       </c>
       <c r="B19">
-        <v>843294</v>
+        <v>845646</v>
       </c>
       <c r="C19">
-        <v>786274</v>
+        <v>776444</v>
       </c>
       <c r="D19">
-        <v>57020</v>
+        <v>69202</v>
       </c>
       <c r="E19">
-        <v>7.251924901497442</v>
+        <v>8.912683979784752</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Catemu</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="B20">
-        <v>834136.5</v>
+        <v>843294</v>
       </c>
       <c r="C20">
-        <v>772736</v>
+        <v>786274</v>
       </c>
       <c r="D20">
-        <v>61400.5</v>
+        <v>57020</v>
       </c>
       <c r="E20">
-        <v>7.945857317376182</v>
+        <v>7.251924901497442</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Zapallar</t>
+          <t>Catemu</t>
         </is>
       </c>
       <c r="B21">
-        <v>833844</v>
+        <v>834136.5</v>
       </c>
       <c r="C21">
-        <v>762500</v>
+        <v>772736</v>
       </c>
       <c r="D21">
-        <v>71344</v>
+        <v>61400.5</v>
       </c>
       <c r="E21">
-        <v>9.35659016393442</v>
+        <v>7.945857317376182</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Zapallar</t>
         </is>
       </c>
       <c r="B22">
-        <v>828127.5</v>
+        <v>833844</v>
       </c>
       <c r="C22">
-        <v>774244</v>
+        <v>762500</v>
       </c>
       <c r="D22">
-        <v>53883.5</v>
+        <v>71344</v>
       </c>
       <c r="E22">
-        <v>6.959498556010768</v>
+        <v>9.35659016393442</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="B23">
-        <v>825240</v>
+        <v>828127.5</v>
       </c>
       <c r="C23">
-        <v>762000</v>
+        <v>774244</v>
       </c>
       <c r="D23">
-        <v>63240</v>
+        <v>53883.5</v>
       </c>
       <c r="E23">
-        <v>8.299212598425187</v>
+        <v>6.959498556010768</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="B24">
-        <v>815320</v>
+        <v>825240</v>
       </c>
       <c r="C24">
-        <v>761650</v>
+        <v>762000</v>
       </c>
       <c r="D24">
-        <v>53670</v>
+        <v>63240</v>
       </c>
       <c r="E24">
-        <v>7.046543688045692</v>
+        <v>8.299212598425187</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>El Tabo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B25">
-        <v>813510</v>
+        <v>815320</v>
       </c>
       <c r="C25">
-        <v>773780</v>
+        <v>761650</v>
       </c>
       <c r="D25">
-        <v>39730</v>
+        <v>53670</v>
       </c>
       <c r="E25">
-        <v>5.134534363772647</v>
+        <v>7.046543688045692</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cabildo</t>
+          <t>El Tabo</t>
         </is>
       </c>
       <c r="B26">
-        <v>809375</v>
+        <v>813510</v>
       </c>
       <c r="C26">
-        <v>749184</v>
+        <v>773780</v>
       </c>
       <c r="D26">
-        <v>60191</v>
+        <v>39730</v>
       </c>
       <c r="E26">
-        <v>8.034207884845369</v>
+        <v>5.134534363772647</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Cabildo</t>
         </is>
       </c>
       <c r="B27">
-        <v>796960</v>
+        <v>809375</v>
       </c>
       <c r="C27">
-        <v>746364</v>
+        <v>749184</v>
       </c>
       <c r="D27">
-        <v>50596</v>
+        <v>60191</v>
       </c>
       <c r="E27">
-        <v>6.778997915226359</v>
+        <v>8.034207884845369</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Puchuncaví</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="B28">
-        <v>787500</v>
+        <v>796960</v>
       </c>
       <c r="C28">
-        <v>735638</v>
+        <v>746364</v>
       </c>
       <c r="D28">
-        <v>51862</v>
+        <v>50596</v>
       </c>
       <c r="E28">
-        <v>7.049934886452314</v>
+        <v>6.778997915226359</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
+          <t>Puchuncaví</t>
         </is>
       </c>
       <c r="B29">
-        <v>781954</v>
+        <v>787500</v>
       </c>
       <c r="C29">
-        <v>737500</v>
+        <v>735638</v>
       </c>
       <c r="D29">
-        <v>44454</v>
+        <v>51862</v>
       </c>
       <c r="E29">
-        <v>6.02766101694916</v>
+        <v>7.049934886452314</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Putaendo</t>
+          <t>Hijuelas</t>
         </is>
       </c>
       <c r="B30">
-        <v>779467.5</v>
+        <v>781954</v>
       </c>
       <c r="C30">
-        <v>718667</v>
+        <v>737500</v>
       </c>
       <c r="D30">
-        <v>60800.5</v>
+        <v>44454</v>
       </c>
       <c r="E30">
-        <v>8.460176966522749</v>
+        <v>6.02766101694916</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Panquehue</t>
+          <t>Putaendo</t>
         </is>
       </c>
       <c r="B31">
-        <v>775000</v>
+        <v>779467.5</v>
       </c>
       <c r="C31">
-        <v>714360</v>
+        <v>718667</v>
       </c>
       <c r="D31">
-        <v>60640</v>
+        <v>60800.5</v>
       </c>
       <c r="E31">
-        <v>8.488717173413974</v>
+        <v>8.460176966522749</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Petorca</t>
+          <t>Panquehue</t>
         </is>
       </c>
       <c r="B32">
-        <v>768021</v>
+        <v>775000</v>
       </c>
       <c r="C32">
-        <v>723020</v>
+        <v>714360</v>
       </c>
       <c r="D32">
-        <v>45001</v>
+        <v>60640</v>
       </c>
       <c r="E32">
-        <v>6.224032530220458</v>
+        <v>8.488717173413974</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Limache</t>
+          <t>Petorca</t>
         </is>
       </c>
       <c r="B33">
-        <v>767100</v>
+        <v>768021</v>
       </c>
       <c r="C33">
-        <v>701440</v>
+        <v>723020</v>
       </c>
       <c r="D33">
-        <v>65660</v>
+        <v>45001</v>
       </c>
       <c r="E33">
-        <v>9.360743613138677</v>
+        <v>6.224032530220458</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Santa María</t>
+          <t>Limache</t>
         </is>
       </c>
       <c r="B34">
-        <v>766130</v>
+        <v>767100</v>
       </c>
       <c r="C34">
-        <v>714130</v>
+        <v>701440</v>
       </c>
       <c r="D34">
-        <v>52000</v>
+        <v>65660</v>
       </c>
       <c r="E34">
-        <v>7.281587386050159</v>
+        <v>9.360743613138677</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Papudo</t>
+          <t>Santa María</t>
         </is>
       </c>
       <c r="B35">
-        <v>747300</v>
+        <v>766130</v>
       </c>
       <c r="C35">
-        <v>705230</v>
+        <v>714130</v>
       </c>
       <c r="D35">
-        <v>42070</v>
+        <v>52000</v>
       </c>
       <c r="E35">
-        <v>5.965429717964343</v>
+        <v>7.281587386050159</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>El Quisco</t>
+          <t>Papudo</t>
         </is>
       </c>
       <c r="B36">
-        <v>737577</v>
+        <v>747300</v>
       </c>
       <c r="C36">
-        <v>675064.5</v>
+        <v>705230</v>
       </c>
       <c r="D36">
-        <v>62512.5</v>
+        <v>42070</v>
       </c>
       <c r="E36">
-        <v>9.260226245047697</v>
+        <v>5.965429717964343</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>El Quisco</t>
         </is>
       </c>
       <c r="B37">
-        <v>737562</v>
+        <v>737577</v>
       </c>
       <c r="C37">
-        <v>691282</v>
+        <v>675064.5</v>
       </c>
       <c r="D37">
-        <v>46280</v>
+        <v>62512.5</v>
       </c>
       <c r="E37">
-        <v>6.694807618309162</v>
+        <v>9.260226245047697</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>La Ligua</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="B38">
-        <v>732483</v>
+        <v>737562</v>
       </c>
       <c r="C38">
-        <v>679413</v>
+        <v>691282</v>
       </c>
       <c r="D38">
-        <v>53070</v>
+        <v>46280</v>
       </c>
       <c r="E38">
-        <v>7.811154629069517</v>
+        <v>6.694807618309162</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>La Ligua</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>732483</v>
+      </c>
+      <c r="C39">
+        <v>679413</v>
+      </c>
+      <c r="D39">
+        <v>53070</v>
+      </c>
+      <c r="E39">
+        <v>7.811154629069517</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Olmué</t>
         </is>
       </c>
-      <c r="B39">
+      <c r="B40">
         <v>727604</v>
       </c>
-      <c r="C39">
+      <c r="C40">
         <v>664640</v>
       </c>
-      <c r="D39">
+      <c r="D40">
         <v>62964</v>
       </c>
-      <c r="E39">
+      <c r="E40">
         <v>9.473399133365422</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2024_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2024_valparaiso.xlsx
@@ -1130,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1139,20 +1139,12 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>846800</v>
+          <t>Rinconada</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1161,48 +1153,33 @@
           <t>Cabildo</t>
         </is>
       </c>
-      <c r="B3">
-        <v>809375</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Calera</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>845646</v>
+          <t>Petorca</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Calle Larga</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>926878</v>
+          <t>Panquehue</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cartagena</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>737562</v>
+          <t>Olmué</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Casablanca</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>828127.5</v>
+          <t>Cartagena</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1211,148 +1188,103 @@
           <t>Catemu</t>
         </is>
       </c>
-      <c r="B8">
-        <v>834136.5</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Concón</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>1153404.5</v>
+          <t>Llaillay</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>El Quisco</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>737577</v>
+          <t>San Felipe</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>El Tabo</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>813510</v>
+          <t>Santa María</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>781954</v>
+          <t>Villa Alemana</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>La Cruz</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>1053000</v>
+          <t>Santo Domingo</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>La Ligua</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>732483</v>
+          <t>San Antonio</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Limache</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>767100</v>
+          <t>El Tabo</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Llaillay</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>897671</v>
+          <t>El Quisco</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Los Andes</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>971396.5</v>
+          <t>Algarrobo</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nogales</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>929430</v>
+          <t>Casablanca</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Olmué</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>727604</v>
+          <t>Valparaíso</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Panquehue</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>775000</v>
+          <t>Viña del Mar</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Papudo</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>747300</v>
+          <t>Concón</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Petorca</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>768021</v>
+          <t>Quintero</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1361,148 +1293,103 @@
           <t>Puchuncaví</t>
         </is>
       </c>
-      <c r="B23">
-        <v>787500</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Putaendo</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>779467.5</v>
+          <t>Zapallar</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quillota</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>846314</v>
+          <t>Papudo</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Quilpué</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>899200</v>
+          <t>La Ligua</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quintero</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>843294</v>
+          <t>Limache</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rinconada</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>932158</v>
+          <t>Quillota</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>796960</v>
+          <t>Calera</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>San Esteban</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>932083</v>
+          <t>Nogales</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>San Felipe</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>825240</v>
+          <t>Calle Larga</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Santa María</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>766130</v>
+          <t>La Cruz</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>976991</v>
+          <t>Putaendo</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>815320</v>
+          <t>San Esteban</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Villa Alemana</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>880539</v>
+          <t>Los Andes</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>886080</v>
+          <t>Hijuelas</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Zapallar</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>833844</v>
+          <t>Quilpué</t>
+        </is>
       </c>
     </row>
   </sheetData>
